--- a/artfynd/A 50808-2025 artfynd.xlsx
+++ b/artfynd/A 50808-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1111,6 +1111,108 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129505689</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80149</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Västra Kolgården, Mpd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>589699</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6932982</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50808-2025 artfynd.xlsx
+++ b/artfynd/A 50808-2025 artfynd.xlsx
@@ -1116,7 +1116,7 @@
         <v>129505689</v>
       </c>
       <c r="B6" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 50808-2025 artfynd.xlsx
+++ b/artfynd/A 50808-2025 artfynd.xlsx
@@ -1116,7 +1116,7 @@
         <v>129505689</v>
       </c>
       <c r="B6" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 50808-2025 artfynd.xlsx
+++ b/artfynd/A 50808-2025 artfynd.xlsx
@@ -1116,7 +1116,7 @@
         <v>129505689</v>
       </c>
       <c r="B6" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 50808-2025 artfynd.xlsx
+++ b/artfynd/A 50808-2025 artfynd.xlsx
@@ -1116,7 +1116,7 @@
         <v>129505689</v>
       </c>
       <c r="B6" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 50808-2025 artfynd.xlsx
+++ b/artfynd/A 50808-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124071407</v>
+        <v>124068927</v>
       </c>
       <c r="B2" t="n">
-        <v>79891</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lunglav, Mpd</t>
+          <t>Ullticka, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589693</v>
+        <v>589743</v>
       </c>
       <c r="R2" t="n">
-        <v>6933011</v>
+        <v>6932931</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2025-04-14</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>14:49</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>14:49</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,62 +760,57 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124071156</v>
+        <v>129505648</v>
       </c>
       <c r="B3" t="n">
-        <v>79891</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lunglav , Mpd</t>
+          <t>Västra Kolgården, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589686</v>
+        <v>589731</v>
       </c>
       <c r="R3" t="n">
-        <v>6933010</v>
+        <v>6933006</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>14:45</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14:45</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,27 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124068927</v>
+        <v>124071156</v>
       </c>
       <c r="B4" t="n">
-        <v>91012</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,34 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ullticka, Mpd</t>
+          <t>Lunglav , Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589743</v>
+        <v>589686</v>
       </c>
       <c r="R4" t="n">
-        <v>6932931</v>
+        <v>6933010</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,9 +937,19 @@
           <t>2025-04-14</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,27 +964,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124735185</v>
+        <v>124071407</v>
       </c>
       <c r="B5" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1037,14 +1007,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Näverbäcken , Mpd</t>
+          <t>Lunglav, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589665</v>
+        <v>589693</v>
       </c>
       <c r="R5" t="n">
-        <v>6933025</v>
+        <v>6933011</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,22 +1041,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129505689</v>
+        <v>124071664</v>
       </c>
       <c r="B6" t="n">
-        <v>80186</v>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1142,21 +1112,16 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Västra Kolgården, Mpd</t>
+          <t>Lunglav , Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589699</v>
+        <v>589703</v>
       </c>
       <c r="R6" t="n">
-        <v>6932982</v>
+        <v>6933013</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,12 +1148,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1203,15 +1178,667 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>124735185</v>
+      </c>
+      <c r="B7" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Näverbäcken , Mpd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>589665</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6933025</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129505689</v>
+      </c>
+      <c r="B8" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Västra Kolgården, Mpd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>589699</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6932982</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
           <t>Joel Helker-Nygren</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>Joel Helker-Nygren</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>124071023</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Spillning tjäder, Mpd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>589645</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6933017</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2 honor 1 hane på platts. Skrämdes iväg</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>124071833</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Spillning tjäder, Mpd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>589653</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6933043</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-04-14</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>124737718</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Näverbäcken , Mpd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>589627</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6933029</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>124738463</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Näverbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>589686</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6933032</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-05-04</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50808-2025 artfynd.xlsx
+++ b/artfynd/A 50808-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,6 +794,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124071023</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -901,6 +911,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124737718</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -998,6 +1013,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124068927</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1095,6 +1115,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129505648</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124071156</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1309,6 +1339,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124071407</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1416,6 +1451,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124071664</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1523,6 +1563,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124735185</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1625,6 +1670,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129505689</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1732,6 +1782,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124071833</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1839,8 +1894,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124738463</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>